--- a/master_akreditasi/data/LAMSPAK-UNGGUL_import.xlsx
+++ b/master_akreditasi/data/LAMSPAK-UNGGUL_import.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ButirDokumen" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ButirDokumen'!$A$1:$J$215</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ButirDokumen'!$A$1:$K$215</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -526,12 +526,36 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Upload: menu Master &gt; Import Excel &gt; instrumen 'LAMSPAK Unggul' &gt; mode UPDATE &gt; Preview &gt; Commit.</t>
+          <t>Kolom kode_bersama: butir dengan kode sama (juga di instrumen lain) memakai dokumen yang sama,</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  cukup diunggah sekali. UNIV-... = dokumen Universitas, UPPS-... = dokumen fakultas/UPPS,</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PRODI-... = dokumen prodi yang diminta di dua standar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Upload: menu Master &gt; Import Excel &gt; instrumen 'LAMSPAK Unggul' &gt; mode UPDATE &gt; Preview &gt; Commit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Sheet Petunjuk ini diabaikan oleh sistem.</t>
         </is>
@@ -849,7 +873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J215"/>
+  <dimension ref="A1:K215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -862,6 +886,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -915,6 +940,11 @@
           <t>panduan_dokumen</t>
         </is>
       </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>kode_bersama</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -961,6 +991,7 @@
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1007,6 +1038,7 @@
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1053,6 +1085,7 @@
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1099,6 +1132,7 @@
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1146,7 +1180,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Dokumen yang sama juga diminta pada butir U5.01 (Standar 5). Unggah file yang sama.</t>
+          <t>Dokumen bersama dengan butir U5.01 (Standar 5): cukup diunggah sekali di salah satu butir, otomatis terhitung di keduanya.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>PRODI-SK-KURIKULUM</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1235,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Dokumen yang sama juga diminta pada butir U5.05 (Standar 5). Unggah file yang sama.</t>
+          <t>Dokumen bersama dengan butir U5.05 (Standar 5): cukup diunggah sekali di salah satu butir, otomatis terhitung di keduanya.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>PRODI-MATRIKS-PROFIL-LULUSAN-CPL</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1290,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Dokumen yang sama juga diminta pada butir U5.06 (Standar 5). Unggah file yang sama.</t>
+          <t>Dokumen bersama dengan butir U5.06 (Standar 5): cukup diunggah sekali di salah satu butir, otomatis terhitung di keduanya.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>PRODI-MATRIKS-CPL-MATA-KULIAH</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1345,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Dokumen yang sama juga diminta pada butir U5.13 (Standar 5). Unggah file yang sama.</t>
+          <t>Dokumen bersama dengan butir U5.13 (Standar 5): cukup diunggah sekali di salah satu butir, otomatis terhitung di keduanya.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>PRODI-LAPORAN-TRACER-STUDY</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1400,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Dokumen yang sama juga diminta pada butir U5.14 (Standar 5). Unggah file yang sama.</t>
+          <t>Dokumen bersama dengan butir U5.14 (Standar 5): cukup diunggah sekali di salah satu butir, otomatis terhitung di keduanya.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>PRODI-SURVEI-PENGGUNA-LULUSAN</t>
         </is>
       </c>
     </row>
@@ -1395,6 +1454,7 @@
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1441,6 +1501,7 @@
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1487,6 +1548,7 @@
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1533,6 +1595,7 @@
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1579,6 +1642,7 @@
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1625,6 +1689,7 @@
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1671,6 +1736,7 @@
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1717,6 +1783,7 @@
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1763,6 +1830,7 @@
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1809,6 +1877,7 @@
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1855,6 +1924,7 @@
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1901,6 +1971,7 @@
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1947,6 +2018,7 @@
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1994,7 +2066,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Dokumen yang sama juga diminta pada butir U5.09 (Standar 5). Unggah file yang sama.</t>
+          <t>Dokumen bersama dengan butir U5.09 (Standar 5): cukup diunggah sekali di salah satu butir, otomatis terhitung di keduanya.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>PRODI-RPS-SELURUH-MATA-KULIAH</t>
         </is>
       </c>
     </row>
@@ -2043,6 +2120,7 @@
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2089,6 +2167,7 @@
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2135,6 +2214,7 @@
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2181,6 +2261,7 @@
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2227,6 +2308,11 @@
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>UNIV-KALENDER-AKADEMIK</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2273,6 +2359,7 @@
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2319,6 +2406,7 @@
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2365,6 +2453,7 @@
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2411,6 +2500,7 @@
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2457,6 +2547,7 @@
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2503,6 +2594,7 @@
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2549,6 +2641,7 @@
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2595,6 +2688,11 @@
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>UNIV-PEDOMAN-MBKM</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2641,6 +2739,7 @@
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2687,6 +2786,7 @@
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2733,6 +2833,7 @@
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2779,6 +2880,7 @@
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2825,6 +2927,11 @@
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>UNIV-PEDOMAN-AKADEMIK</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2871,6 +2978,11 @@
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>UNIV-SOP-PENILAIAN-PEMBELAJARAN</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2917,6 +3029,7 @@
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2963,6 +3076,7 @@
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3009,6 +3123,7 @@
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3055,6 +3170,7 @@
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3101,6 +3217,7 @@
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3147,6 +3264,7 @@
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3193,6 +3311,7 @@
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3239,6 +3358,7 @@
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3285,6 +3405,7 @@
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3331,6 +3452,7 @@
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3377,6 +3499,7 @@
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3423,6 +3546,7 @@
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3469,6 +3593,11 @@
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>UPPS-SK-STRUKTUR-ORGANISASI-UPPS</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3515,6 +3644,11 @@
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>UNIV-DOKUMEN-SOTK</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3561,6 +3695,11 @@
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>UPPS-URAIAN-TUGAS-PIMPINAN-DAN-UNIT-KERJA</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3607,6 +3746,11 @@
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>UPPS-SOP-TATA-KELOLA</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3653,6 +3797,11 @@
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>UPPS-DOKUMEN-RENSTRA-UPPS</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3699,6 +3848,7 @@
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3745,6 +3895,7 @@
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3791,6 +3942,11 @@
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>UPPS-LAPORAN-KINERJA-UPPS-PS</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3837,6 +3993,7 @@
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3883,6 +4040,7 @@
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3929,6 +4087,7 @@
         </is>
       </c>
       <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3975,6 +4134,7 @@
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4021,6 +4181,7 @@
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4067,6 +4228,11 @@
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>UNIV-PEDOMAN-ETIKA-AKADEMIK</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4113,6 +4279,11 @@
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>UNIV-SOP-PENERIMAAN-MAHASISWA-BARU</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4159,6 +4330,7 @@
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4205,6 +4377,7 @@
         </is>
       </c>
       <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4251,6 +4424,11 @@
         </is>
       </c>
       <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>UNIV-SOP-LAYANAN-MAHASISWA</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4297,6 +4475,7 @@
         </is>
       </c>
       <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4343,6 +4522,7 @@
         </is>
       </c>
       <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4390,7 +4570,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Dokumen yang sama juga diminta pada butir U1.05 (Standar 1). Unggah file yang sama.</t>
+          <t>Dokumen bersama dengan butir U1.05 (Standar 1): cukup diunggah sekali di salah satu butir, otomatis terhitung di keduanya.</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>PRODI-SK-KURIKULUM</t>
         </is>
       </c>
     </row>
@@ -4439,6 +4624,7 @@
         </is>
       </c>
       <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4485,6 +4671,7 @@
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4531,6 +4718,7 @@
         </is>
       </c>
       <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4578,7 +4766,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Dokumen yang sama juga diminta pada butir U1.06 (Standar 1). Unggah file yang sama.</t>
+          <t>Dokumen bersama dengan butir U1.06 (Standar 1): cukup diunggah sekali di salah satu butir, otomatis terhitung di keduanya.</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>PRODI-MATRIKS-PROFIL-LULUSAN-CPL</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4821,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Dokumen yang sama juga diminta pada butir U1.07 (Standar 1). Unggah file yang sama.</t>
+          <t>Dokumen bersama dengan butir U1.07 (Standar 1): cukup diunggah sekali di salah satu butir, otomatis terhitung di keduanya.</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>PRODI-MATRIKS-CPL-MATA-KULIAH</t>
         </is>
       </c>
     </row>
@@ -4677,6 +4875,7 @@
         </is>
       </c>
       <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4723,6 +4922,7 @@
         </is>
       </c>
       <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4770,7 +4970,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Dokumen yang sama juga diminta pada butir U2.01 (Standar 2). Unggah file yang sama.</t>
+          <t>Dokumen bersama dengan butir U2.01 (Standar 2): cukup diunggah sekali di salah satu butir, otomatis terhitung di keduanya.</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>PRODI-RPS-SELURUH-MATA-KULIAH</t>
         </is>
       </c>
     </row>
@@ -4819,6 +5024,7 @@
         </is>
       </c>
       <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4865,6 +5071,7 @@
         </is>
       </c>
       <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4911,6 +5118,7 @@
         </is>
       </c>
       <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4958,7 +5166,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Dokumen yang sama juga diminta pada butir U1.08 (Standar 1). Unggah file yang sama.</t>
+          <t>Dokumen bersama dengan butir U1.08 (Standar 1): cukup diunggah sekali di salah satu butir, otomatis terhitung di keduanya.</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>PRODI-LAPORAN-TRACER-STUDY</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5221,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Dokumen yang sama juga diminta pada butir U1.09 (Standar 1). Unggah file yang sama.</t>
+          <t>Dokumen bersama dengan butir U1.09 (Standar 1): cukup diunggah sekali di salah satu butir, otomatis terhitung di keduanya.</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>PRODI-SURVEI-PENGGUNA-LULUSAN</t>
         </is>
       </c>
     </row>
@@ -5057,6 +5275,7 @@
         </is>
       </c>
       <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5103,6 +5322,7 @@
         </is>
       </c>
       <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5149,6 +5369,7 @@
         </is>
       </c>
       <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5195,6 +5416,7 @@
         </is>
       </c>
       <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5241,6 +5463,7 @@
         </is>
       </c>
       <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5287,6 +5510,7 @@
         </is>
       </c>
       <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5333,6 +5557,7 @@
         </is>
       </c>
       <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5379,6 +5604,7 @@
         </is>
       </c>
       <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5425,6 +5651,7 @@
         </is>
       </c>
       <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5471,6 +5698,7 @@
         </is>
       </c>
       <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5517,6 +5745,7 @@
         </is>
       </c>
       <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5563,6 +5792,7 @@
         </is>
       </c>
       <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5609,6 +5839,7 @@
         </is>
       </c>
       <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5655,6 +5886,7 @@
         </is>
       </c>
       <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5701,6 +5933,7 @@
         </is>
       </c>
       <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5747,6 +5980,7 @@
         </is>
       </c>
       <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5793,6 +6027,7 @@
         </is>
       </c>
       <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5839,6 +6074,7 @@
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5885,6 +6121,7 @@
         </is>
       </c>
       <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5931,6 +6168,7 @@
         </is>
       </c>
       <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5977,6 +6215,7 @@
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6023,6 +6262,7 @@
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6069,6 +6309,11 @@
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>UPPS-SK-TENAGA-KEPENDIDIKAN</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6115,6 +6360,11 @@
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>UPPS-IJAZAH-TENAGA-KEPENDIDIKAN</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6161,6 +6411,11 @@
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>UPPS-SERTIFIKAT-PELATIHAN-TENDIK</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6207,6 +6462,11 @@
         </is>
       </c>
       <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>UPPS-DOKUMEN-PENGEMBANGAN-DOSEN-DAN-TENDIK</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6253,6 +6513,11 @@
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>UPPS-DAFTAR-INVENTARIS-SARANA-PRASARANA</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6299,6 +6564,11 @@
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>UPPS-FOTO-RUANG-KULIAH</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6345,6 +6615,7 @@
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6391,6 +6662,11 @@
         </is>
       </c>
       <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>UPPS-FOTO-LABORATORIUM</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6437,6 +6713,11 @@
         </is>
       </c>
       <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>UPPS-DAFTAR-PERALATAN-LABORATORIUM</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6483,6 +6764,11 @@
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>UPPS-SOP-PENGGUNAAN-LABORATORIUM</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6529,6 +6815,11 @@
         </is>
       </c>
       <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>UPPS-JADWAL-PENGGUNAAN-LABORATORIUM</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6575,6 +6866,11 @@
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>UPPS-MODUL-PRAKTIKUM-PANDUAN-PRAKTIK</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6621,6 +6917,11 @@
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>UNIV-DAFTAR-KOLEKSI-PERPUSTAKAAN</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6667,6 +6968,11 @@
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>UNIV-DATA-AKSES-JURNAL-E-BOOK</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6713,6 +7019,11 @@
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>UNIV-SCREENSHOT-REPOSITORY-DIGITAL-LIBRARY</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6759,6 +7070,11 @@
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>UNIV-SCREENSHOT-LMS</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6805,6 +7121,11 @@
         </is>
       </c>
       <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>UNIV-SCREENSHOT-SIAKAD</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6851,6 +7172,11 @@
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>UNIV-DATA-BANDWIDTH-INTERNET</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6897,6 +7223,11 @@
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>UNIV-LAPORAN-PEMELIHARAAN-SARPRAS</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6943,6 +7274,11 @@
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>UNIV-BERITA-ACARA-PERBAIKAN-PENGADAAN</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6989,6 +7325,11 @@
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>UNIV-DOKUMEN-K3</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7035,6 +7376,11 @@
         </is>
       </c>
       <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>UPPS-FOTO-APAR-JALUR-EVAKUASI</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7081,6 +7427,11 @@
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>UNIV-DOKUMEN-PENGELOLAAN-SAMPAH-LIMBAH</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7127,6 +7478,11 @@
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>UNIV-FOTO-FASILITAS-AKSESIBILITAS</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7173,6 +7529,11 @@
         </is>
       </c>
       <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>UPPS-RKA-RKAT-UPPS</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7219,6 +7580,7 @@
         </is>
       </c>
       <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7265,6 +7627,11 @@
         </is>
       </c>
       <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>UPPS-LAPORAN-REALISASI-ANGGARAN</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7311,6 +7678,11 @@
         </is>
       </c>
       <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>UPPS-LAPORAN-DANA-OPERASIONAL-PENDIDIKAN</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7357,6 +7729,11 @@
         </is>
       </c>
       <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>UPPS-LAPORAN-DANA-KEMAHASISWAAN</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7403,6 +7780,11 @@
         </is>
       </c>
       <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>UNIV-LAPORAN-DANA-PENELITIAN</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7449,6 +7831,11 @@
         </is>
       </c>
       <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>UNIV-LAPORAN-DANA-PKM</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7495,6 +7882,11 @@
         </is>
       </c>
       <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>UNIV-SK-PENERIMA-DANA-PENELITIAN</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7541,6 +7933,11 @@
         </is>
       </c>
       <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>UNIV-SK-PENERIMA-DANA-PKM</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7587,6 +7984,7 @@
         </is>
       </c>
       <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7633,6 +8031,11 @@
         </is>
       </c>
       <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>UPPS-BUKTI-INVESTASI-SDM</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7679,6 +8082,11 @@
         </is>
       </c>
       <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>UPPS-BUKTI-INVESTASI-SARANA</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7725,6 +8133,11 @@
         </is>
       </c>
       <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>UPPS-BUKTI-INVESTASI-PRASARANA</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7771,6 +8184,11 @@
         </is>
       </c>
       <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>UPPS-LAPORAN-PERTANGGUNGJAWABAN-KEUANGAN</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7817,6 +8235,11 @@
         </is>
       </c>
       <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>UNIV-DOKUMEN-AUDIT-LAPORAN-PEMERIKSAAN-KEUANGAN</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7863,6 +8286,11 @@
         </is>
       </c>
       <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>UPPS-NOTULEN-RAPAT-ANGGARAN</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7909,6 +8337,11 @@
         </is>
       </c>
       <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>UPPS-DOKUMEN-ESTIMASI-SUMBER-PENDANAAN</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7955,6 +8388,7 @@
         </is>
       </c>
       <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8001,6 +8435,7 @@
         </is>
       </c>
       <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8047,6 +8482,11 @@
         </is>
       </c>
       <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>UNIV-PEDOMAN-PENELITIAN</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8093,6 +8533,7 @@
         </is>
       </c>
       <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8139,6 +8580,7 @@
         </is>
       </c>
       <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8185,6 +8627,7 @@
         </is>
       </c>
       <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8231,6 +8674,7 @@
         </is>
       </c>
       <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8277,6 +8721,7 @@
         </is>
       </c>
       <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8323,6 +8768,7 @@
         </is>
       </c>
       <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8369,6 +8815,7 @@
         </is>
       </c>
       <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8415,6 +8862,7 @@
         </is>
       </c>
       <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8461,6 +8909,7 @@
         </is>
       </c>
       <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8507,6 +8956,7 @@
         </is>
       </c>
       <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8553,6 +9003,7 @@
         </is>
       </c>
       <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8599,6 +9050,7 @@
         </is>
       </c>
       <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8645,6 +9097,7 @@
         </is>
       </c>
       <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8691,6 +9144,7 @@
         </is>
       </c>
       <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8737,6 +9191,7 @@
         </is>
       </c>
       <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8783,6 +9238,7 @@
         </is>
       </c>
       <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8829,6 +9285,11 @@
         </is>
       </c>
       <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>UNIV-PEDOMAN-PKM</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8875,6 +9336,7 @@
         </is>
       </c>
       <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8921,6 +9383,7 @@
         </is>
       </c>
       <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8967,6 +9430,7 @@
         </is>
       </c>
       <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9013,6 +9477,7 @@
         </is>
       </c>
       <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9059,6 +9524,7 @@
         </is>
       </c>
       <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9105,6 +9571,7 @@
         </is>
       </c>
       <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9151,6 +9618,7 @@
         </is>
       </c>
       <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9197,6 +9665,7 @@
         </is>
       </c>
       <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9243,6 +9712,7 @@
         </is>
       </c>
       <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9289,6 +9759,7 @@
         </is>
       </c>
       <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9335,6 +9806,7 @@
         </is>
       </c>
       <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9381,6 +9853,7 @@
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9427,6 +9900,7 @@
         </is>
       </c>
       <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9473,6 +9947,7 @@
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9519,6 +9994,7 @@
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9565,6 +10041,7 @@
         </is>
       </c>
       <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9611,6 +10088,11 @@
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>UNIV-SK-LEMBAGA-PENJAMINAN-MUTU</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9657,6 +10139,11 @@
         </is>
       </c>
       <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>UPPS-SK-UNIT-PENJAMINAN-MUTU-UPPS-PS</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -9703,6 +10190,11 @@
         </is>
       </c>
       <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>UNIV-STRUKTUR-ORGANISASI-MUTU</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9749,6 +10241,11 @@
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>UNIV-KEBIJAKAN-SPMI</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9795,6 +10292,11 @@
         </is>
       </c>
       <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>UNIV-MANUAL-SPMI</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9841,6 +10343,11 @@
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>UNIV-STANDAR-SPMI</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9887,6 +10394,11 @@
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>UNIV-FORMULIR-SPMI</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9933,6 +10445,11 @@
         </is>
       </c>
       <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>UNIV-SOP-MUTU</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -9979,6 +10496,11 @@
         </is>
       </c>
       <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>UNIV-DOKUMEN-PENETAPAN-STANDAR</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10025,6 +10547,7 @@
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10071,6 +10594,7 @@
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10117,6 +10641,7 @@
         </is>
       </c>
       <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10163,6 +10688,11 @@
         </is>
       </c>
       <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>UNIV-SK-AUDITOR-MUTU-INTERNAL</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10209,6 +10739,11 @@
         </is>
       </c>
       <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>UNIV-INSTRUMEN-AMI</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10255,6 +10790,7 @@
         </is>
       </c>
       <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10301,6 +10837,7 @@
         </is>
       </c>
       <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10347,6 +10884,11 @@
         </is>
       </c>
       <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>UPPS-NOTULEN-RTM</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10393,6 +10935,11 @@
         </is>
       </c>
       <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>UPPS-DAFTAR-HADIR-RTM</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10439,6 +10986,11 @@
         </is>
       </c>
       <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>UPPS-LAPORAN-TINDAK-LANJUT-RTM</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10485,6 +11037,7 @@
         </is>
       </c>
       <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10531,6 +11084,7 @@
         </is>
       </c>
       <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10577,6 +11131,11 @@
         </is>
       </c>
       <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>UNIV-DASHBOARD-SISTEM-INFORMASI-MUTU</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -10623,6 +11182,7 @@
         </is>
       </c>
       <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10669,6 +11229,7 @@
         </is>
       </c>
       <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10715,6 +11276,7 @@
         </is>
       </c>
       <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10761,6 +11323,7 @@
         </is>
       </c>
       <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10807,9 +11370,10 @@
         </is>
       </c>
       <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J215"/>
+  <autoFilter ref="A1:K215"/>
   <dataValidations count="4">
     <dataValidation sqref="D2:D215" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"UNIVERSITAS,BIRO,FAKULTAS,PRODI"</formula1>

--- a/master_akreditasi/data/LAMSPAK-UNGGUL_import.xlsx
+++ b/master_akreditasi/data/LAMSPAK-UNGGUL_import.xlsx
@@ -2066,7 +2066,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Dokumen bersama dengan butir U5.09 (Standar 5): cukup diunggah sekali di salah satu butir, otomatis terhitung di keduanya.</t>
+          <t>Tidak perlu unggah: RPS yang disahkan di SI-OBE masuk otomatis (1 dokumen per MK). Berlaku juga untuk butir U5.09.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2119,8 +2119,16 @@
           <t>Bukti kedalaman dan keluasan pembelajaran bidang keilmuan program studi</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Tidak perlu unggah: pilih MK penciri dari RPS yang sudah disahkan di SI-OBE pada halaman butir ini. Berlaku juga untuk butir U5.10.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>PRODI-RPS-MK-PENCIRI</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4970,7 +4978,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Dokumen bersama dengan butir U2.01 (Standar 2): cukup diunggah sekali di salah satu butir, otomatis terhitung di keduanya.</t>
+          <t>Tidak perlu unggah: RPS yang disahkan di SI-OBE masuk otomatis (1 dokumen per MK). Berlaku juga untuk butir U2.01.</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5023,8 +5031,16 @@
           <t>Bukti kekhasan keilmuan program studi</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Tidak perlu unggah: pilih MK penciri dari RPS yang sudah disahkan di SI-OBE pada halaman butir ini. Berlaku juga untuk butir U2.02.</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>PRODI-RPS-MK-PENCIRI</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">

--- a/master_akreditasi/data/LAMSPAK-UNGGUL_import.xlsx
+++ b/master_akreditasi/data/LAMSPAK-UNGGUL_import.xlsx
@@ -3554,7 +3554,11 @@
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>PRODI-SCREENSHOT-INPUT-NILAI-SIAKAD</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
